--- a/SWR302/reference/SE_SWP_TopicList_SP26.xlsx
+++ b/SWR302/reference/SE_SWP_TopicList_SP26.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Snake\FU\Teach\Material\SWP391\Assignment\Topic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fptu\SWR302\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F314B7-4386-432D-A1C5-1AB49D18BC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Topic" sheetId="1" r:id="rId1"/>
@@ -476,7 +477,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -600,9 +601,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -641,6 +639,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -857,66 +858,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD13"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="33" style="13" customWidth="1"/>
-    <col min="4" max="5" width="13.6640625" style="13" customWidth="1"/>
-    <col min="6" max="6" width="34.6640625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="35" style="13" customWidth="1"/>
-    <col min="8" max="8" width="20.21875" style="13" customWidth="1"/>
-    <col min="9" max="9" width="95.88671875" style="13" customWidth="1"/>
-    <col min="10" max="11" width="31" style="13" customWidth="1"/>
-    <col min="12" max="30" width="8.6640625" style="13" customWidth="1"/>
-    <col min="31" max="16384" width="14.44140625" style="13"/>
+    <col min="1" max="1" width="3.109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="33" style="12" customWidth="1"/>
+    <col min="4" max="5" width="13.6640625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="34.6640625" style="12" customWidth="1"/>
+    <col min="7" max="7" width="35" style="12" customWidth="1"/>
+    <col min="8" max="8" width="20.21875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="95.88671875" style="12" customWidth="1"/>
+    <col min="10" max="10" width="30" style="12" customWidth="1"/>
+    <col min="11" max="11" width="44.33203125" style="12" customWidth="1"/>
+    <col min="12" max="30" width="8.6640625" style="12" customWidth="1"/>
+    <col min="31" max="16384" width="14.44140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="36" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -925,449 +927,449 @@
       <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-    </row>
-    <row r="3" spans="1:30" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+    </row>
+    <row r="3" spans="1:30" ht="216" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
+      <c r="J3" s="2"/>
+      <c r="K3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
     </row>
     <row r="4" spans="1:30" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4" t="s">
+      <c r="J4" s="2"/>
+      <c r="K4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
     </row>
     <row r="5" spans="1:30" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
     </row>
     <row r="6" spans="1:30" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
     </row>
     <row r="7" spans="1:30" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
     </row>
     <row r="8" spans="1:30" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="5"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B12" s="6"/>
+      <c r="B12" s="5"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B13" s="6"/>
+      <c r="B13" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K4" r:id="rId1"/>
+    <hyperlink ref="K4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1375,7 +1377,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -1390,129 +1392,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>15</v>
       </c>
     </row>
@@ -1522,7 +1524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -1537,127 +1539,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>15</v>
       </c>
     </row>
@@ -1667,7 +1669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -1682,129 +1684,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>15</v>
       </c>
     </row>
@@ -1814,7 +1816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -1829,129 +1831,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>15</v>
       </c>
     </row>
@@ -1961,7 +1963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -1976,129 +1978,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>15</v>
       </c>
     </row>
@@ -2108,7 +2110,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -2123,129 +2125,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>15</v>
       </c>
     </row>
@@ -2255,7 +2257,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -2270,129 +2272,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>15</v>
       </c>
     </row>

--- a/SWR302/reference/SE_SWP_TopicList_SP26.xlsx
+++ b/SWR302/reference/SE_SWP_TopicList_SP26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fptu\SWR302\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F314B7-4386-432D-A1C5-1AB49D18BC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1956F238-6A34-442F-9A7C-DDC5C0C18A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/SWR302/reference/SE_SWP_TopicList_SP26.xlsx
+++ b/SWR302/reference/SE_SWP_TopicList_SP26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fptu\SWR302\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1956F238-6A34-442F-9A7C-DDC5C0C18A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453B2B2F-0860-47A6-8FC3-705F8522FE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/SWR302/reference/SE_SWP_TopicList_SP26.xlsx
+++ b/SWR302/reference/SE_SWP_TopicList_SP26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fptu\SWR302\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453B2B2F-0860-47A6-8FC3-705F8522FE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9234134-9159-41FE-B30E-2C3125463775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -936,7 +936,7 @@
       <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="15" t="s">
         <v>17</v>
       </c>
       <c r="J2" s="2"/>

--- a/SWR302/reference/SE_SWP_TopicList_SP26.xlsx
+++ b/SWR302/reference/SE_SWP_TopicList_SP26.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fptu\SWR302\reference\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Snake\FU\Teach\Material\SWP391\Assignment\Topic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9234134-9159-41FE-B30E-2C3125463775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
   </bookViews>
   <sheets>
     <sheet name="Topic" sheetId="1" r:id="rId1"/>
@@ -32,9 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="79">
-  <si>
-    <t>#</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="113">
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
   <si>
     <t>Code</t>
@@ -212,7 +211,6 @@
         <sz val="11"/>
         <color rgb="FF0563C1"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">https://justcleanrecycling.ng/product/citizen-waste-reporting-app/
 </t>
@@ -223,7 +221,6 @@
         <sz val="11"/>
         <color rgb="FF1155CC"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>https://www.reciclos.com/en/
 https://candam.eu/candam-waste-intelligence-citizen-app/</t>
@@ -354,8 +351,8 @@
 </t>
   </si>
   <si>
-    <t>-Seller: Chức năng chính: Đăng tin bán xe (ảnh, video, mô tả chi tiết), Quản lý tin đăng (sửa, ẩn, xóa), Nhận &amp; trả lời tin nhắn từ người mua, Quản lý đơn đặt mua / đặt cọc, Xem đánh giá uy tín'
-- Buyer: Đăng ký / đăng nhập, Tìm kiếm &amp; lọc xe (loại xe, giá, hãng, kích thước khung, tình trạng), Xem chi tiết xe (ảnh, mô tả, lịch sử sử dụng), Nhắn tin / chat với người bán, Đặt mua / đặt cọc, Đánh giá người bán sau giao dịch, Lưu xe yêu thích (wishlist).
+    <t>-Seller: Chức năng chính: Đăng tin bán xe (ảnh, video, mô tả chi tiết), Quản lý tin đăng (sửa, ẩn, xóa), Quản lý đơn đặt mua / đặt cọc, Xem đánh giá uy tín'
+- Buyer: Đăng ký / đăng nhập, Tìm kiếm &amp; lọc xe (loại xe, giá, hãng, kích thước khung, tình trạng), Xem chi tiết xe (ảnh, mô tả, lịch sử sử dụng), Đặt mua / đặt cọc, Đánh giá sản phẩm sau giao dịch, Lưu xe yêu thích (wishlist).
 - Inspector: Kiểm tra tình trạng xe (khung, phanh, truyền động), Gắn nhãn “Xe đã kiểm định”, 
 Upload báo cáo kiểm định, Hỗ trợ giải quyết tranh chấp
 - Admin: Quản lý người dùng (buyer, seller): Kiểm duyệt tin đăng, Xử lý báo cáo vi phạm / tranh chấp, Quản lý danh mục xe, thương hiệu, Quản lý giao dịch &amp; phí dịch vụ, Thống kê &amp; báo cáo hệ thống.
@@ -401,17 +398,17 @@
 - Xem tồn kho hiện tại tại cửa hàng
 Central Kitchen Staff
 - Tiếp nhận và xử lý đơn đặt hàng từ các cửa hàng franchise
-- Lập kế hoạch sản xuất theo nhu cầu tổng hợp
+(Optional)- Lập kế hoạch sản xuất theo nhu cầu tổng hợp
 - Cập nhật trạng thái sản xuất và xuất kho
 - Quản lý nguyên liệu đầu vào, hạn sử dụng và lô sản xuất
 Supply Coordinator
 - Tổng hợp và phân loại đơn đặt hàng từ các cửa hàng
-- Điều phối sản xuất và phân phối hàng hóa
-- Lập lịch giao hàng và theo dõi tiến độ vận chuyển
+(Optional)- Điều phối sản xuất và phân phối hàng hóa
+(Optional)- Lập lịch giao hàng và theo dõi tiến độ vận chuyển
 - Xử lý các vấn đề phát sinh (thiếu hàng, giao trễ, hủy đơn)
 Manager
 - Quản lý danh mục sản phẩm, công thức và định mức nguyên liệu
-- Quản lý tồn kho bếp trung tâm và cửa hàng
+(Optional)- Quản lý tồn kho bếp trung tâm và cửa hàng
 - Theo dõi hiệu suất sản xuất, phân phối và bán hàng
 - Thống kê, báo cáo chi phí, hao hụt và hiệu quả vận hành
 Admin
@@ -457,13 +454,238 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Một Citizen được tạo tối đa bao nhiêu yêu cầu đồng thời?</t>
+  </si>
+  <si>
+    <t>01 yêu cầu, chỉ được tạo yêu cầu mới khi yêu cầu trước đã hoàn tất hoặc bị hủy.</t>
+  </si>
+  <si>
+    <t>Trạng thái chuẩn của yêu cầu gồm những trạng thái nào?</t>
+  </si>
+  <si>
+    <t>Pending (Mới tạo), Verified (Đã xác minh), In Progress (Đang xử lý), Completed (Hoàn tất), Cancelled (Hủy), Duplicate (Trùng lặp)</t>
+  </si>
+  <si>
+    <t>Mức độ khẩn cấp được phân loại theo bao nhiêu cấp?</t>
+  </si>
+  <si>
+    <t>High: Nguy hiểm tính mạng ngay
+ Medium: Nguy cơ cao, chưa khẩn cấp tức thì
+ Low: Hỗ trợ khi có điều kiện</t>
+  </si>
+  <si>
+    <t>Quy tắc ưu tiên xử lý khi nhiều yêu cầu cùng lúc?</t>
+  </si>
+  <si>
+    <t>Ưu tiên theo thứ tự:
+ 1. Mức độ khẩn cấp
+ 2. Số người bị ảnh hưởng
+ 3. Thời gian tạo yêu cầu</t>
+  </si>
+  <si>
+    <t>Một Rescue Team xử lý tối đa bao nhiêu nhiệm vụ song song?</t>
+  </si>
+  <si>
+    <t>Tùy theo điều phối của Rescue Coordinator</t>
+  </si>
+  <si>
+    <t>Phân biệt cứu hộ và cứu trợ (hàng hóa) ra sao?</t>
+  </si>
+  <si>
+    <t>Cứu hộ: Giải cứu con người khỏi nguy hiểm trực tiếp
+Cứu trợ: Phân phối hàng cứu trợ sau khi đã an toàn</t>
+  </si>
+  <si>
+    <t>Ai chịu trách nhiệm xác nhận phân phối hàng?</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>Quy tắc xử lý yêu cầu trùng lặp?</t>
+  </si>
+  <si>
+    <t>Hệ thống phát hiện theo vị trí + thời gian + Citizen
+Rescue Coordinator xác nhận
+Yêu cầu trùng được gắn trạng thái Duplicate và liên kết với yêu cầu chính</t>
+  </si>
+  <si>
+    <t>Có cho phép tạo yêu cầu thay mặt Citizen?</t>
+  </si>
+  <si>
+    <t>Có, do Rescue Coordinator tạo</t>
+  </si>
+  <si>
+    <t>Khi dữ liệu vị trí không chính xác, xử lý ra sao?</t>
+  </si>
+  <si>
+    <t>Rescue Coordinator sẽ thực hiện chỉnh sửa, đánh dấu yêu cầu là Location Unverified cho đến khi xác nhận</t>
+  </si>
+  <si>
     <t>Nền tảng kết nối người dân, doanh nghiệp tái chế và dịch vụ thu gom rác theo khu vực.</t>
   </si>
   <si>
+    <t>Một báo cáo rác có thể được nhiều doanh nghiệp xem hay chỉ một? Thời gian tối đa từ Accepted → Collected là bao lâu? Điều kiện nào xác định báo cáo là “hợp lệ” để nhận điểm? Một Công dân có giới hạn số báo cáo/ngày không? Xử lý thế nào với báo cáo trùng lặp cùng vị trí? Điểm thưởng có bị trừ nếu phân loại sai? Collector có thể từ chối nhiệm vụ đã được gán không? Có SLA bắt buộc cho từng loại rác không? Doanh nghiệp có được ưu tiên yêu cầu theo hợp đồng không? Trạng thái nào cho phép khiếu nại? Một báo cáo có thể bị huỷ bởi ai? Cách xử lý khi Collector không cập nhật trạng thái? Có cơ chế phạt doanh nghiệp không hoàn thành cam kết không? Điểm thưởng có hết hạn không? Có bảng xếp hạng theo thời gian (tuần/tháng/năm) không?</t>
+  </si>
+  <si>
+    <t>Nhiều doanh nghiệp cùng xem, nhưng chỉ 1 doanh nghiệp Accepted.
+Tùy theo loại rác/khu vực
+Tham khảo checklist: Ảnh rõ + GPS trong bán kính cho phép+ loại rác được chọn + khối lượng tối thiểu + không trùng/không spam + được Enterprise xác nhận
+Nên giới hạn ≤N báo cáo/ngày để chống spam
+Định nghĩa “trùng” bằng ngưỡng: khoảng cách GPS ≤R mét và thời gian ≤T phút và cùng loại rác: giữ report đầu, những report sau bị đánh dấu duplicate.</t>
+  </si>
+  <si>
+    <t>Công dân có thể chỉnh sửa báo cáo sau khi gửi không? Doanh nghiệp có thể cấu hình nhiều bộ quy tắc điểm song song không? Có cơ chế kiểm duyệt ảnh trước khi hiển thị không? Có cho phép Collector cập nhật offline không? Khi AI gợi ý sai, hệ thống ghi nhận thế nào? Có cơ chế chống gian lận điểm không? Một Collector có thể thuộc nhiều doanh nghiệp không?</t>
+  </si>
+  <si>
+    <t>Cho sửa trước Accepted; sau Accepted chỉ cho bổ sung thông tin
+Effective date + chỉ 1 rule set active tại 1 thời điểm
+Chỉ cộng điểm sau khi Collected thành công
+1 Collector–1 Enterprise (dễ kiểm soát)</t>
+  </si>
+  <si>
     <t>Phần mềm hỗ trợ gán nhãn dữ liệu</t>
   </si>
   <si>
+    <t>Cách tính chất lượng gán nhãn (precision/recall/IAA)
+Ngưỡng chất lượng tối thiểu để xuất dữ liệu?
+Phân loại lỗi gồm những loại nào, ai định nghĩa?
+Thứ tự ưu tiên duyệt dữ liệu được xác định ra sao?</t>
+  </si>
+  <si>
+    <t>- Nhãn là do Annotator gán nên sẽ không có ground truth để tính precision/recall. Về cơ bản nhóm có thể dùng quy tắc đa số để quyết định nhãn. Ví dụ: 2/3 người cùng gán nhãn A thì mẫu đó được gán nhãn A. Tùy vào khả năng của nhóm mà có thể dùng thêm chỉ số đồng thuận Kappa để quyết định xem một mẫu sẽ có nhãn gì. Từ đó, chỉ xuất những mẫu có chỉ số đồng thuận Kappa lớn hơn xx%, (xx có thể do Manager tùy chỉnh).
+- Hiện tại có thể dùng textbox để ghi nhận lỗi, hoặc tùy vào khả năng của nhóm và bài toán mà nhóm định nghĩa để có thể phát triển thêm. Ví dụ: Bài toán phân lớp ảnh thì nếu ảnh con chó mà gán nhãn con mèo là lỗi. Bài toán phân đoạn ảnh thì có thể dùng độ đo Intersection over Union (IoU)...
+- Nhóm có thể thêm deadline cho mỗi dự án gán nhãn, hoặc thêm mức độ quan trọng của dự án để xác định thứ tự duyệt.</t>
+  </si>
+  <si>
+    <t>Pre-order có yêu cầu đặt cọc tối thiểu % không?
+Combo gọng + tròng tính giá theo rule nào?
+Có phân tuyến đơn theo kho/kỹ thuật không?
+Điều kiện từ chối đơn prescription là gì?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Pre-order có yêu cầu đặt cọc tối thiểu % không?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; Pre-order cần yêu cầu đặc cọc hoặc trả full trước;
+=&gt; % đặt cọc tối thiểu là bao nhiêu, tùy vào business rule của Nhóm quy định. Business rule có thể linh động config/thay đổi được trong trang quản trị.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Combo gọng + tròng tính giá theo rule nào?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">=&gt; Tùy vào business rule của Nhóm quy định. Manager có thể setup giá theo gọng kính riêng, tròng kính riêng, combo gọng + tròng riêng theo loại kính và tròng; hoặc theo các đợt sự kiện, khuyến mãi.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Có phân tuyến đơn theo kho/kỹ thuật không?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+=&gt; Tùy phạm vi đề tài. Nếu hệ thống có nhiều chi nhánh cửa hàng, Khách hàng có thể chọn đặt làm kính theo chi nhánh.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Điều kiện từ chối đơn prescription là gì?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>=&gt; Câu hỏi chưa rõ.</t>
+    </r>
+  </si>
+  <si>
+    <t>Đặt cọc tối thiểu/tối đa bao nhiêu % giá xe?
+Khi buyer hủy cọc, xử lý tiền cọc thế nào?
+Khi seller hủy giao dịch, chế tài ra sao?
+Một xe có thể nhận nhiều yêu cầu đặt cọc song song không?
+Thứ tự ưu tiên khi nhiều buyer đặt mua?
+Điều kiện để gắn nhãn “Xe đã kiểm định”?
+Ai chịu phí kiểm định?
+Có cho phép cửa hàng xe đạp tham gia với vai trò seller không?
+Seller cá nhân và cửa hàng có chính sách khác nhau không?</t>
+  </si>
+  <si>
+    <t>Khi xảy ra tranh chấp giữa người mua và người bán thì bên kiểm định có những trách nhiệm hay cơ sở nào giải quyết tranh chấp</t>
+  </si>
+  <si>
     <t>Hệ thống Quản lý Bếp Trung Tâm và Cửa hàng Franchise</t>
+  </si>
+  <si>
+    <t>Trong quá trình giao hàng bị lỗi thì ai chịu trách nhiệm? Hàng tồn kho cuối ngày của cửa hàng xử lý thế nào?</t>
+  </si>
+  <si>
+    <t>Lỗi khi chưa giao thì central kitchen chịu.
+Lỗi khi giao thì bên giao hàng chịu.
+Sau khi bàn giao cho cửa hàng mà lỗi thì cửa hàng chịu, còn cửa hàng kiểm tra mà phát hiện lỗi khi nhận hàng thì trả lại feedback ngược.
+Hàng tồn cuối ngày thì xử lý theo hạn sử dụng (còn hạn thì dùng tiếp, hết hạn thì bỏ, sắp hết hạn thì có chính sách khuyển mãi)</t>
+  </si>
+  <si>
+    <t>Ưu tiên xử lý đơn theo tiêu chí nào (thời gian, doanh thu, khu vực)?
+Có cho phép sửa/hủy đơn sau khi đã xác nhận không?
+Điều kiện nào để Central Kitchen từ chối đơn?
+Cách xử lý khi thiếu nguyên liệu cho đơn đã xác nhận?
+Có backorder hay tách giao nhiều đợt không?
+Định mức nguyên liệu có sai số cho phép?
+Có quy tắc phân bổ hàng khi nguồn cung thiếu?
+Quy tắc gom đơn theo tuyến giao hàng?</t>
+  </si>
+  <si>
+    <t>Ưu tiên xử lý đơn theo thời gian cần để giao hàng và độ quan trong của cửa hàng (doanh thu cao, hoặc cửa hàng ưu tiên do mới mở)
+Đơn sau khi xác nhận nếu chưa sản xuất thì cho huỷ, đã hoăc đang sản xuất thì không cho huỷ.
+Central Kitchen từ chối đơn khi không đủ nguyên liệu, hoặc yêu cầu thời gian không hợp lý, hoặc cửa hàng đang nợ tiền chưa trả.
+Khi thiếu nguyên liệu cho đơn đã tiếp nhận thì tìm nguồn cung thay thế, hoặc tách làm nhiều đơn, hoặc làm 1 phần đơn.
+Backorder hay không tuỳ vào business rules của nhóm. 
+Có thể có sai số cho phép trong khoảng +-2-5%. Nếu xuất kho hoặc hao hụt vượt ngưỡng thì báo Manager.
+Khi nguồn cung thiếu thì ưu tiên theo đơn đã xác nhận, cửa hàng doanh thu cao, có thể chọn cấp đủ cho 1 cửa hàng hoặc chia đều cho nhiều cửa hàng.
+Nên để bên thứ 3 gom đơn giao hàng, vì nếu làm phần này nữa thì Scope của SWP khá lớn.</t>
   </si>
   <si>
     <t>Hệ thống bán kính mắt trực tuyến, hỗ trợ mua kính có sẵn, đặt trước hoặc làm kính theo nhu cầu
@@ -477,7 +699,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -486,38 +708,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -525,34 +724,45 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF1155CC"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -596,52 +806,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -858,67 +1065,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD13"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="33" style="12" customWidth="1"/>
-    <col min="4" max="5" width="13.6640625" style="12" customWidth="1"/>
-    <col min="6" max="6" width="34.6640625" style="12" customWidth="1"/>
-    <col min="7" max="7" width="35" style="12" customWidth="1"/>
-    <col min="8" max="8" width="20.21875" style="12" customWidth="1"/>
-    <col min="9" max="9" width="95.88671875" style="12" customWidth="1"/>
-    <col min="10" max="10" width="30" style="12" customWidth="1"/>
-    <col min="11" max="11" width="44.33203125" style="12" customWidth="1"/>
-    <col min="12" max="30" width="8.6640625" style="12" customWidth="1"/>
-    <col min="31" max="16384" width="14.44140625" style="12"/>
+    <col min="1" max="1" width="5.44140625" style="14" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="33" style="14" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="34.6640625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="35" style="14" customWidth="1"/>
+    <col min="8" max="8" width="22.5546875" style="14" customWidth="1"/>
+    <col min="9" max="9" width="95.88671875" style="14" customWidth="1"/>
+    <col min="10" max="11" width="31" style="14" customWidth="1"/>
+    <col min="12" max="30" width="8.6640625" style="14" customWidth="1"/>
+    <col min="31" max="16384" width="14.44140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="36" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:30" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -927,449 +1134,449 @@
       <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-    </row>
-    <row r="3" spans="1:30" ht="216" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+    </row>
+    <row r="3" spans="1:30" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="15" t="s">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
     </row>
     <row r="4" spans="1:30" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="3" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
     </row>
     <row r="5" spans="1:30" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="5"/>
-      <c r="AA5" s="5"/>
-      <c r="AB5" s="5"/>
-      <c r="AC5" s="5"/>
-      <c r="AD5" s="5"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="6"/>
+      <c r="AB5" s="6"/>
+      <c r="AC5" s="6"/>
+      <c r="AD5" s="6"/>
     </row>
     <row r="6" spans="1:30" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="5"/>
-      <c r="AD6" s="5"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="6"/>
+      <c r="AB6" s="6"/>
+      <c r="AC6" s="6"/>
+      <c r="AD6" s="6"/>
     </row>
     <row r="7" spans="1:30" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
-      <c r="AB7" s="5"/>
-      <c r="AC7" s="5"/>
-      <c r="AD7" s="5"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
     </row>
     <row r="8" spans="1:30" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
-      <c r="AB8" s="5"/>
-      <c r="AC8" s="5"/>
-      <c r="AD8" s="5"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="6"/>
+      <c r="AD8" s="6"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
-      <c r="AB9" s="5"/>
-      <c r="AC9" s="5"/>
-      <c r="AD9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="5"/>
-      <c r="AD11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B12" s="5"/>
+      <c r="B12" s="6"/>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="B13" s="5"/>
+      <c r="B13" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K4" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1377,146 +1584,287 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="54.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="21.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="14"/>
+    <col min="2" max="2" width="24.6640625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="54.88671875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="16" style="14" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="14" customWidth="1"/>
+    <col min="6" max="7" width="14.44140625" style="14"/>
+    <col min="8" max="8" width="76.44140625" style="14" customWidth="1"/>
+    <col min="9" max="16384" width="14.44140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+    </row>
+    <row r="2" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="C3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="C4" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="C5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
+      <c r="C6" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="9" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="C7" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
+      <c r="C8" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="9" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="C9" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
+      <c r="C10" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="9" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="C11" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
+      <c r="C12" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="9" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
         <v>15</v>
       </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1524,7 +1872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -1539,54 +1887,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
@@ -1669,144 +2017,159 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L17"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="60.44140625" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="21.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="14"/>
+    <col min="2" max="2" width="24.6640625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="60.44140625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="16" style="14" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="14" customWidth="1"/>
+    <col min="6" max="7" width="14.44140625" style="14"/>
+    <col min="8" max="8" width="90.77734375" style="14" customWidth="1"/>
+    <col min="9" max="16384" width="14.44140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="C1" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+    </row>
+    <row r="2" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+    </row>
+    <row r="3" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="C3" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="C4" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+    <row r="14" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+    <row r="15" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+    <row r="16" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+    <row r="17" spans="1:1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
         <v>15</v>
       </c>
     </row>
@@ -1816,144 +2179,153 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="21.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="14"/>
+    <col min="2" max="2" width="24.6640625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="16" style="14" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="14" customWidth="1"/>
+    <col min="6" max="7" width="14.44140625" style="14"/>
+    <col min="8" max="8" width="53.6640625" style="14" customWidth="1"/>
+    <col min="9" max="16384" width="14.44140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="C1" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+    </row>
+    <row r="2" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+    </row>
+    <row r="3" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
+      <c r="C3" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="A17" s="10">
         <v>15</v>
       </c>
     </row>
@@ -1963,144 +2335,153 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="65.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="21.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="14"/>
+    <col min="2" max="2" width="24.6640625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="65.88671875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="16" style="14" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="14" customWidth="1"/>
+    <col min="6" max="7" width="14.44140625" style="14"/>
+    <col min="8" max="8" width="61" style="14" customWidth="1"/>
+    <col min="9" max="16384" width="14.44140625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+    </row>
+    <row r="2" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+    </row>
+    <row r="3" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
+      <c r="C3" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="A17" s="10">
         <v>15</v>
       </c>
     </row>
@@ -2110,144 +2491,153 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="65.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="21.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="14"/>
+    <col min="2" max="2" width="24.6640625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="65.88671875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="16" style="14" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="14" customWidth="1"/>
+    <col min="6" max="7" width="14.44140625" style="14"/>
+    <col min="8" max="8" width="21.88671875" style="14" customWidth="1"/>
+    <col min="9" max="16384" width="14.44140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+    </row>
+    <row r="2" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+    </row>
+    <row r="3" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="C3" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
+      <c r="C4" s="10" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="A17" s="10">
         <v>15</v>
       </c>
     </row>
@@ -2257,144 +2647,160 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="65.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="21.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" style="14"/>
+    <col min="2" max="2" width="19.33203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="65.88671875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="14" customWidth="1"/>
+    <col min="6" max="6" width="7.6640625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="68.88671875" style="14" customWidth="1"/>
+    <col min="9" max="16384" width="14.44140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="C1" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+    </row>
+    <row r="2" spans="1:12" ht="42" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+    </row>
+    <row r="3" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="C3" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="216" x14ac:dyDescent="0.3">
+      <c r="A4" s="10">
         <v>2</v>
       </c>
+      <c r="C4" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="10">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="A12" s="10">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="10">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="A14" s="10">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="10">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="10">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="A17" s="10">
         <v>15</v>
       </c>
     </row>
